--- a/Data/Export/Common/Title_爵位.xlsx
+++ b/Data/Export/Common/Title_爵位.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882F9B31-2F4B-460B-A2D3-9E69E0AA4D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D350ED27-9AE8-4D04-8F71-0D837447E752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12300" yWindow="3870" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="1095" windowWidth="21600" windowHeight="11355" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Titles" sheetId="36" r:id="rId1"/>
@@ -65,35 +65,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>皇帝</t>
+  </si>
+  <si>
+    <t>王</t>
+  </si>
+  <si>
+    <t>公</t>
+  </si>
+  <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i32</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>皇帝</t>
-  </si>
-  <si>
-    <t>王</t>
-  </si>
-  <si>
-    <t>公</t>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>指挥</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -141,26 +137,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -657,7 +655,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>5</v>
@@ -706,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
@@ -724,32 +722,32 @@
         <v>1</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.15">
@@ -757,7 +755,7 @@
         <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2">
         <v>11000</v>
@@ -765,9 +763,6 @@
       <c r="E6" s="2">
         <v>1</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -776,10 +771,10 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A7" s="3"/>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="2">
         <v>11000</v>
@@ -787,9 +782,6 @@
       <c r="E7" s="2">
         <v>9</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -797,20 +789,17 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2">
         <v>6</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -818,20 +807,17 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2">
         <v>2</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -839,10 +825,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="2">
         <v>13000</v>
@@ -850,9 +836,6 @@
       <c r="E10" s="2">
         <v>5</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -860,10 +843,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2">
         <v>13000</v>
@@ -871,9 +854,6 @@
       <c r="E11" s="2">
         <v>7</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -881,20 +861,17 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2">
         <v>3</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -902,20 +879,17 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.15">
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2">
         <v>4</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -926,26 +900,20 @@
         <v>36</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2">
         <v>8</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
